--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:11</t>
+          <t>2026-09-09 00:50:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:12</t>
+          <t>2026-09-09 00:50:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:14</t>
+          <t>2026-09-09 00:50:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:15</t>
+          <t>2026-09-09 00:50:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:15</t>
+          <t>2026-09-09 00:50:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:15</t>
+          <t>2026-09-09 00:50:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:15</t>
+          <t>2026-09-09 00:50:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:37:15</t>
+          <t>2026-09-09 00:50:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:21</t>
+          <t>2026-09-09 01:15:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:22</t>
+          <t>2026-09-09 01:15:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:23</t>
+          <t>2026-09-09 01:15:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:25</t>
+          <t>2026-09-09 01:15:48</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:25</t>
+          <t>2026-09-09 01:15:48</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:25</t>
+          <t>2026-09-09 01:15:48</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:25</t>
+          <t>2026-09-09 01:15:48</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 00:50:25</t>
+          <t>2026-09-09 01:15:48</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.80%3,800,000</t>
+          <t>11.76%3,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.76%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.27%1,380,000</t>
+          <t>9.31%1,380,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.27%</t>
+          <t>9.31%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.71%531</t>
+          <t>-1.51%523</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>9.21%13,800,000</t>
+          <t>9.06%13,800,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.06%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.87%500,000</t>
+          <t>7.78%500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>7.78%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.85%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.00%5,000,000</t>
+          <t>6.23%5,000,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>6.23%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2327國巨股份</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.74%567</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>567</v>
+        <v>4625</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.35%7,500,000</t>
+          <t>5.81%1,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.35%</t>
+          <t>5.81%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>7500000</v>
+        <v>1000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>2327國巨股份</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-0.35%565</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4710</v>
+        <v>565</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.33%900,000</t>
+          <t>5.32%7,500,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>900000</v>
+        <v>7500000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.16%1,250,000</t>
+          <t>5.30%1,250,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.16%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6669緯穎科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2340</v>
+        <v>1110</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.09%1,730,020</t>
+          <t>4.53%3,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>4.53%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1730020</v>
+        <v>3250000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>6669緯穎科技</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1025</v>
+        <v>2325</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.19%3,250,000</t>
+          <t>4.38%1,500,020</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.19%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3250000</v>
+        <v>1500020</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.6%800</t>
+          <t>+1.5%812</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.12%4,100,000</t>
+          <t>4.18%4,100,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.18%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,33 +1180,33 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1955</v>
+        <v>2015</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.56%1,450,000</t>
+          <t>3.42%1,350,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.42%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1450000</v>
+        <v>1350000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>19220</v>
+        <v>18605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.40%140,500</t>
+          <t>3.28%140,500</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.24%900,000</t>
+          <t>3.22%900,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.22%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:44</t>
+          <t>2026-09-09 19:32:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1345</v>
+        <v>5615</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.04%1,800,000</t>
+          <t>3.17%450,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1800000</v>
+        <v>450000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3026禾伸堂企</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>+1.47%758</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5795</v>
+        <v>758</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.77%380,000</t>
+          <t>2.57%2,700,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>380000</v>
+        <v>2700000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3026禾伸堂企</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.11%747</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>747</v>
+        <v>1345</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.54%2,700,000</t>
+          <t>2.53%1,500,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.53%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2700000</v>
+        <v>1500000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>3653健策精密</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.17%6970</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.17%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6970</v>
+        <v>5760</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.45%280,000</t>
+          <t>2.46%340,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.46%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>280000</v>
+        <v>340000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3653健策精密</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>-3.59%6720</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5550</v>
+        <v>6720</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.37%340,000</t>
+          <t>2.36%280,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>340000</v>
+        <v>280000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.48%2085</t>
+          <t>0%2085</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>618</v>
+        <v>640</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.61%328</t>
+          <t>+4.27%342</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.76%251.5</t>
+          <t>+0.2%252</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.72%229</t>
+          <t>+2.18%234</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>+2.18%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1805</v>
+        <v>1795</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.33%186.5</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:45</t>
+          <t>2026-09-09 19:33:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.56%152</t>
+          <t>+3.29%157</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.33%149</t>
+          <t>-1.34%147</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.1%968</t>
+          <t>+1.14%979</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.87%113.5</t>
+          <t>-2.64%110.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>113.5</v>
+        <v>110.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+0.57%70.6</t>
+          <t>-1.27%69.7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0%692</t>
+          <t>+1.88%705</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.88%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.19%68.2</t>
+          <t>-2.35%66.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.19%</t>
+          <t>-2.35%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>68.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.83%484</t>
+          <t>+5.17%509</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+4.59%45.55</t>
+          <t>-1.77%44.35</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+4.59%</t>
+          <t>-1.77%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>45.55</v>
+        <v>44.35</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,11 +2849,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.8%50.6</t>
+          <t>-0.59%50.3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.8%45.15</t>
+          <t>-0.93%42.4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>45.15</v>
+        <v>42.4</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.95%37.3</t>
+          <t>-0.58%43.2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>-0.58%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>37.3</v>
+        <v>43.2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.14%42.8</t>
+          <t>-1.47%36.75</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.14%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>42.8</v>
+        <v>36.75</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,21 +3127,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+2%43.45</t>
+          <t>-2.85%44.25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>43.45</v>
+        <v>44.25</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:47</t>
+          <t>2026-09-09 19:33:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>268.5</v>
+        <v>270</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:48</t>
+          <t>2026-09-09 19:33:02</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-3.75%231</t>
+          <t>-1.3%228</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:48</t>
+          <t>2026-09-09 19:33:02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2912統一超商</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.93%217</t>
+          <t>+1.06%191.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>217</v>
+        <v>191.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:48</t>
+          <t>2026-09-09 19:33:02</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2912統一超商</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.56%189.5</t>
+          <t>+0.23%217.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>189.5</v>
+        <v>217.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:48</t>
+          <t>2026-09-09 19:33:02</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.72%139</t>
+          <t>+0.36%139.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+0.36%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>139</v>
+        <v>139.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 01:15:48</t>
+          <t>2026-09-09 19:33:02</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.99%76.7</t>
+          <t>-0.91%76</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>76.7</v>
+        <v>76</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:32:59</t>
+          <t>2026-09-09 22:36:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:00</t>
+          <t>2026-09-09 22:36:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:01</t>
+          <t>2026-09-09 22:36:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:02</t>
+          <t>2026-09-09 22:36:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:02</t>
+          <t>2026-09-09 22:36:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:02</t>
+          <t>2026-09-09 22:36:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:02</t>
+          <t>2026-09-09 22:36:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:02</t>
+          <t>2026-09-09 22:36:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:21</t>
+          <t>2026-09-09 22:47:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:23</t>
+          <t>2026-09-09 22:47:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:24</t>
+          <t>2026-09-09 22:47:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:25</t>
+          <t>2026-09-09 22:47:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:25</t>
+          <t>2026-09-09 22:47:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:25</t>
+          <t>2026-09-09 22:47:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:25</t>
+          <t>2026-09-09 22:47:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:36:25</t>
+          <t>2026-09-09 22:47:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:27</t>
+          <t>2026-09-09 23:09:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:28</t>
+          <t>2026-09-09 23:09:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:29</t>
+          <t>2026-09-09 23:09:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:31</t>
+          <t>2026-09-09 23:09:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:31</t>
+          <t>2026-09-09 23:09:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:31</t>
+          <t>2026-09-09 23:09:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:31</t>
+          <t>2026-09-09 23:09:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-09 22:47:31</t>
+          <t>2026-09-09 23:09:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
